--- a/data/nzd0591/nzd0591.xlsx
+++ b/data/nzd0591/nzd0591.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L499"/>
+  <dimension ref="A1:L502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21324,7 +21324,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>276.6</v>
+        <v>265.8</v>
       </c>
       <c r="C499" t="n">
         <v>161.69</v>
@@ -21354,6 +21354,132 @@
         <v>190.8</v>
       </c>
       <c r="L499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>235.4</v>
+      </c>
+      <c r="C500" t="n">
+        <v>160.81</v>
+      </c>
+      <c r="D500" t="n">
+        <v>148.39</v>
+      </c>
+      <c r="E500" t="n">
+        <v>138.99</v>
+      </c>
+      <c r="F500" t="n">
+        <v>140</v>
+      </c>
+      <c r="G500" t="n">
+        <v>140.47</v>
+      </c>
+      <c r="H500" t="n">
+        <v>144.32</v>
+      </c>
+      <c r="I500" t="n">
+        <v>198.67</v>
+      </c>
+      <c r="J500" t="n">
+        <v>184.82</v>
+      </c>
+      <c r="K500" t="n">
+        <v>191.86</v>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:43+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>220.44</v>
+      </c>
+      <c r="C501" t="n">
+        <v>160.57</v>
+      </c>
+      <c r="D501" t="n">
+        <v>149.17</v>
+      </c>
+      <c r="E501" t="n">
+        <v>139.1</v>
+      </c>
+      <c r="F501" t="n">
+        <v>140.48</v>
+      </c>
+      <c r="G501" t="n">
+        <v>141.54</v>
+      </c>
+      <c r="H501" t="n">
+        <v>144.81</v>
+      </c>
+      <c r="I501" t="n">
+        <v>201.59</v>
+      </c>
+      <c r="J501" t="n">
+        <v>184.63</v>
+      </c>
+      <c r="K501" t="n">
+        <v>192.99</v>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>213.1</v>
+      </c>
+      <c r="C502" t="n">
+        <v>161.04</v>
+      </c>
+      <c r="D502" t="n">
+        <v>149.82</v>
+      </c>
+      <c r="E502" t="n">
+        <v>140.16</v>
+      </c>
+      <c r="F502" t="n">
+        <v>141.14</v>
+      </c>
+      <c r="G502" t="n">
+        <v>141.93</v>
+      </c>
+      <c r="H502" t="n">
+        <v>145.39</v>
+      </c>
+      <c r="I502" t="n">
+        <v>202.07</v>
+      </c>
+      <c r="J502" t="n">
+        <v>185.28</v>
+      </c>
+      <c r="K502" t="n">
+        <v>193.16</v>
+      </c>
+      <c r="L502" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21370,7 +21496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26513,6 +26639,36 @@
       </c>
       <c r="B514" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>
@@ -26675,28 +26831,28 @@
         <v>0.1396</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6421084816070167</v>
+        <v>-0.6309689047962711</v>
       </c>
       <c r="J2" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="K2" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01983601027606063</v>
+        <v>0.019435899493499</v>
       </c>
       <c r="M2" t="n">
-        <v>28.13083352072644</v>
+        <v>28.01706945330286</v>
       </c>
       <c r="N2" t="n">
-        <v>1147.289183907313</v>
+        <v>1139.184674566428</v>
       </c>
       <c r="O2" t="n">
-        <v>33.87165753114709</v>
+        <v>33.75180994504485</v>
       </c>
       <c r="P2" t="n">
-        <v>227.2949840220542</v>
+        <v>227.1744213217168</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26747,28 +26903,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1684174262155964</v>
+        <v>-0.170572441291737</v>
       </c>
       <c r="J3" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="K3" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04618532003379383</v>
+        <v>0.04788900513130911</v>
       </c>
       <c r="M3" t="n">
-        <v>4.124621614670421</v>
+        <v>4.110198059295548</v>
       </c>
       <c r="N3" t="n">
-        <v>33.28143852368787</v>
+        <v>33.10239203932726</v>
       </c>
       <c r="O3" t="n">
-        <v>5.769006718984462</v>
+        <v>5.753467827260986</v>
       </c>
       <c r="P3" t="n">
-        <v>167.201412136476</v>
+        <v>167.2244924850616</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26819,28 +26975,28 @@
         <v>0.0935</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3486284404948246</v>
+        <v>-0.3465819196532921</v>
       </c>
       <c r="J4" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="K4" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L4" t="n">
-        <v>0.393937464117323</v>
+        <v>0.3938220456959199</v>
       </c>
       <c r="M4" t="n">
-        <v>2.64195027678908</v>
+        <v>2.6356671376921</v>
       </c>
       <c r="N4" t="n">
-        <v>10.62389506823188</v>
+        <v>10.58039304860872</v>
       </c>
       <c r="O4" t="n">
-        <v>3.259431709398416</v>
+        <v>3.252751611883195</v>
       </c>
       <c r="P4" t="n">
-        <v>156.7851655375498</v>
+        <v>156.7632395383905</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26891,28 +27047,28 @@
         <v>0.0799</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4197819693189144</v>
+        <v>-0.4180827836822409</v>
       </c>
       <c r="J5" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="K5" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4469793686254331</v>
+        <v>0.4479522113862151</v>
       </c>
       <c r="M5" t="n">
-        <v>2.750515910659237</v>
+        <v>2.742851713919026</v>
       </c>
       <c r="N5" t="n">
-        <v>12.38709332482289</v>
+        <v>12.32705800243559</v>
       </c>
       <c r="O5" t="n">
-        <v>3.519530270479697</v>
+        <v>3.510991028532484</v>
       </c>
       <c r="P5" t="n">
-        <v>149.2929262739048</v>
+        <v>149.274720299025</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26963,28 +27119,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.224527954113232</v>
+        <v>-0.2259954308058565</v>
       </c>
       <c r="J6" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="K6" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1830391917102193</v>
+        <v>0.1868660784810103</v>
       </c>
       <c r="M6" t="n">
-        <v>2.762609712578065</v>
+        <v>2.755255775021078</v>
       </c>
       <c r="N6" t="n">
-        <v>12.78397651404795</v>
+        <v>12.71805814787849</v>
       </c>
       <c r="O6" t="n">
-        <v>3.575468712497419</v>
+        <v>3.566238655485425</v>
       </c>
       <c r="P6" t="n">
-        <v>147.8626710344991</v>
+        <v>147.8783840350787</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27035,28 +27191,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2116069558355702</v>
+        <v>-0.2148307093003888</v>
       </c>
       <c r="J7" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="K7" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1906510558268598</v>
+        <v>0.1967502985938898</v>
       </c>
       <c r="M7" t="n">
-        <v>2.476323720150705</v>
+        <v>2.480677478311446</v>
       </c>
       <c r="N7" t="n">
-        <v>10.80001754831763</v>
+        <v>10.78245809928696</v>
       </c>
       <c r="O7" t="n">
-        <v>3.286338014921415</v>
+        <v>3.283665345202973</v>
       </c>
       <c r="P7" t="n">
-        <v>149.7881434576013</v>
+        <v>149.8226675652306</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27107,28 +27263,28 @@
         <v>0.1121</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2953017776366506</v>
+        <v>-0.2970320082807545</v>
       </c>
       <c r="J8" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="K8" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2378271202194683</v>
+        <v>0.2422022068690267</v>
       </c>
       <c r="M8" t="n">
-        <v>2.943217988803547</v>
+        <v>2.932039565377446</v>
       </c>
       <c r="N8" t="n">
-        <v>15.87786953633582</v>
+        <v>15.79689113366367</v>
       </c>
       <c r="O8" t="n">
-        <v>3.984704447802349</v>
+        <v>3.974530303528163</v>
       </c>
       <c r="P8" t="n">
-        <v>154.2959897990436</v>
+        <v>154.3145175039525</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27179,28 +27335,28 @@
         <v>0.0152</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5953953519174271</v>
+        <v>-0.6026238051777998</v>
       </c>
       <c r="J9" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="K9" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1038893996940594</v>
+        <v>0.1072745805552945</v>
       </c>
       <c r="M9" t="n">
-        <v>9.643076675197202</v>
+        <v>9.622379655208764</v>
       </c>
       <c r="N9" t="n">
-        <v>175.5554933147883</v>
+        <v>174.7301777188055</v>
       </c>
       <c r="O9" t="n">
-        <v>13.24973559414633</v>
+        <v>13.21855429760779</v>
       </c>
       <c r="P9" t="n">
-        <v>223.0470552007299</v>
+        <v>223.1243535149641</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27251,28 +27407,28 @@
         <v>0.1327</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03926524694327892</v>
+        <v>-0.04317979410512523</v>
       </c>
       <c r="J10" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="K10" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006799207905049953</v>
+        <v>0.008275420887454144</v>
       </c>
       <c r="M10" t="n">
-        <v>2.682956258256283</v>
+        <v>2.687994733441079</v>
       </c>
       <c r="N10" t="n">
-        <v>12.88897482818065</v>
+        <v>12.87825985502603</v>
       </c>
       <c r="O10" t="n">
-        <v>3.590121840297436</v>
+        <v>3.588629244575988</v>
       </c>
       <c r="P10" t="n">
-        <v>189.3244027923959</v>
+        <v>189.3662660344063</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27323,28 +27479,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06348975958328489</v>
+        <v>-0.06535273059483994</v>
       </c>
       <c r="J11" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="K11" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0186877601688531</v>
+        <v>0.02000809078666366</v>
       </c>
       <c r="M11" t="n">
-        <v>2.693528018880471</v>
+        <v>2.685654105422368</v>
       </c>
       <c r="N11" t="n">
-        <v>12.02041026551431</v>
+        <v>11.96469191837365</v>
       </c>
       <c r="O11" t="n">
-        <v>3.467046331607686</v>
+        <v>3.459001578255444</v>
       </c>
       <c r="P11" t="n">
-        <v>195.9698554244175</v>
+        <v>195.9898699362302</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27382,7 +27538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L499"/>
+  <dimension ref="A1:L502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58169,7 +58325,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>-46.902232602976575,168.14482497600918</t>
+          <t>-46.90223364643453,168.1446834232305</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -58218,6 +58374,192 @@
         </is>
       </c>
       <c r="L499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-09 22:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-46.902236582631474,168.1442849784168</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-46.90296244313024,168.1433186956276</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-46.90368230284042,168.14316725367485</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-46.904401871014755,168.1430553908227</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-46.905120435490055,168.14307997258774</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-46.90583917614885,168.1430974781081</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-46.90655745876119,168.14315928555942</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>-46.907270766164636,168.14388304439382</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>-46.90799079291077,168.14371284903743</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>-46.90870874906436,168.1438164802024</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:43+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-46.902238027038,168.14408890165117</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-46.90296246627696,168.14331554997</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-46.90368222763165,168.1431774771987</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-46.90440186041058,168.143056832621</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-46.905120389218915,168.14308626415564</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-46.9058390707753,168.1431115032146</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-46.90655741050594,168.14316570835808</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>-46.90727047837335,168.14392131955597</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>-46.90799081163152,168.1437103584971</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>-46.90870863938771,168.14383129258943</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-46.90223873560075,168.1439926982172</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-46.90296242094787,168.14332171021618</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-46.90368216495698,168.14318599680192</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-46.90440175822393,168.14307072631357</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-46.90512032559554,168.14309491506154</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-46.90583903236768,168.1431166151693</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-46.906557353387,168.14317331085448</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>-46.90727043106396,168.14392761136352</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>-46.907990747586645,168.14371887876675</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>-46.90870862288752,168.14383352100165</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0591/nzd0591.xlsx
+++ b/data/nzd0591/nzd0591.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L502"/>
+  <dimension ref="A1:L504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21482,6 +21482,90 @@
       <c r="L502" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:27:02+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>208.08</v>
+      </c>
+      <c r="C503" t="n">
+        <v>161.41</v>
+      </c>
+      <c r="D503" t="n">
+        <v>149.85</v>
+      </c>
+      <c r="E503" t="n">
+        <v>140.13</v>
+      </c>
+      <c r="F503" t="n">
+        <v>140.86</v>
+      </c>
+      <c r="G503" t="n">
+        <v>142.17</v>
+      </c>
+      <c r="H503" t="n">
+        <v>145.62</v>
+      </c>
+      <c r="I503" t="n">
+        <v>203.23</v>
+      </c>
+      <c r="J503" t="n">
+        <v>185.21</v>
+      </c>
+      <c r="K503" t="n">
+        <v>193.71</v>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>204.56</v>
+      </c>
+      <c r="C504" t="n">
+        <v>161.87</v>
+      </c>
+      <c r="D504" t="n">
+        <v>150.85</v>
+      </c>
+      <c r="E504" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="F504" t="n">
+        <v>141.18</v>
+      </c>
+      <c r="G504" t="n">
+        <v>142.32</v>
+      </c>
+      <c r="H504" t="n">
+        <v>145.23</v>
+      </c>
+      <c r="I504" t="n">
+        <v>202.44</v>
+      </c>
+      <c r="J504" t="n">
+        <v>184.64</v>
+      </c>
+      <c r="K504" t="n">
+        <v>192.96</v>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21496,7 +21580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26669,6 +26753,26 @@
       </c>
       <c r="B517" t="n">
         <v>0.41</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -26831,28 +26935,28 @@
         <v>0.1396</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6309689047962711</v>
+        <v>-0.633921789194921</v>
       </c>
       <c r="J2" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K2" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L2" t="n">
-        <v>0.019435899493499</v>
+        <v>0.01978263775027655</v>
       </c>
       <c r="M2" t="n">
-        <v>28.01706945330286</v>
+        <v>27.91910966567953</v>
       </c>
       <c r="N2" t="n">
-        <v>1139.184674566428</v>
+        <v>1134.659956917109</v>
       </c>
       <c r="O2" t="n">
-        <v>33.75180994504485</v>
+        <v>33.68471399488364</v>
       </c>
       <c r="P2" t="n">
-        <v>227.1744213217168</v>
+        <v>227.206494295376</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26903,28 +27007,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.170572441291737</v>
+        <v>-0.171318035615845</v>
       </c>
       <c r="J3" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K3" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04788900513130911</v>
+        <v>0.04868630909075433</v>
       </c>
       <c r="M3" t="n">
-        <v>4.110198059295548</v>
+        <v>4.097404415895702</v>
       </c>
       <c r="N3" t="n">
-        <v>33.10239203932726</v>
+        <v>32.97462331504667</v>
       </c>
       <c r="O3" t="n">
-        <v>5.753467827260986</v>
+        <v>5.742353464830137</v>
       </c>
       <c r="P3" t="n">
-        <v>167.2244924850616</v>
+        <v>167.2325058879367</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26975,28 +27079,28 @@
         <v>0.0935</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3465819196532921</v>
+        <v>-0.3442778348188497</v>
       </c>
       <c r="J4" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K4" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3938220456959199</v>
+        <v>0.391917632940217</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6356671376921</v>
+        <v>2.635847447524972</v>
       </c>
       <c r="N4" t="n">
-        <v>10.58039304860872</v>
+        <v>10.574077975958</v>
       </c>
       <c r="O4" t="n">
-        <v>3.252751611883195</v>
+        <v>3.251780739219359</v>
       </c>
       <c r="P4" t="n">
-        <v>156.7632395383905</v>
+        <v>156.7384706878854</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27047,28 +27151,28 @@
         <v>0.0799</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4180827836822409</v>
+        <v>-0.4161379690041014</v>
       </c>
       <c r="J5" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K5" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4479522113862151</v>
+        <v>0.447300828222438</v>
       </c>
       <c r="M5" t="n">
-        <v>2.742851713919026</v>
+        <v>2.742009891072001</v>
       </c>
       <c r="N5" t="n">
-        <v>12.32705800243559</v>
+        <v>12.30327054124856</v>
       </c>
       <c r="O5" t="n">
-        <v>3.510991028532484</v>
+        <v>3.507601821935974</v>
       </c>
       <c r="P5" t="n">
-        <v>149.274720299025</v>
+        <v>149.253813948845</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27119,28 +27223,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2259954308058565</v>
+        <v>-0.2265675509855387</v>
       </c>
       <c r="J6" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K6" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1868660784810103</v>
+        <v>0.1889448147521705</v>
       </c>
       <c r="M6" t="n">
-        <v>2.755255775021078</v>
+        <v>2.747881289771138</v>
       </c>
       <c r="N6" t="n">
-        <v>12.71805814787849</v>
+        <v>12.66973770017501</v>
       </c>
       <c r="O6" t="n">
-        <v>3.566238655485425</v>
+        <v>3.55945750082439</v>
       </c>
       <c r="P6" t="n">
-        <v>147.8783840350787</v>
+        <v>147.8845330569851</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27191,28 +27295,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2148307093003888</v>
+        <v>-0.2161932589730642</v>
       </c>
       <c r="J7" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K7" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1967502985938898</v>
+        <v>0.1999709599343968</v>
       </c>
       <c r="M7" t="n">
-        <v>2.480677478311446</v>
+        <v>2.478950975612968</v>
       </c>
       <c r="N7" t="n">
-        <v>10.78245809928696</v>
+        <v>10.75176820256141</v>
       </c>
       <c r="O7" t="n">
-        <v>3.283665345202973</v>
+        <v>3.278988899426379</v>
       </c>
       <c r="P7" t="n">
-        <v>149.8226675652306</v>
+        <v>149.8373132852091</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27263,28 +27367,28 @@
         <v>0.1121</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2970320082807545</v>
+        <v>-0.2976870738176314</v>
       </c>
       <c r="J8" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K8" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2422022068690267</v>
+        <v>0.2445891664842199</v>
       </c>
       <c r="M8" t="n">
-        <v>2.932039565377446</v>
+        <v>2.922804780091113</v>
       </c>
       <c r="N8" t="n">
-        <v>15.79689113366367</v>
+        <v>15.73702816330013</v>
       </c>
       <c r="O8" t="n">
-        <v>3.974530303528163</v>
+        <v>3.966992332145367</v>
       </c>
       <c r="P8" t="n">
-        <v>154.3145175039525</v>
+        <v>154.3215596343467</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27335,28 +27439,28 @@
         <v>0.0152</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6026238051777998</v>
+        <v>-0.6056959357609428</v>
       </c>
       <c r="J9" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K9" t="n">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1072745805552945</v>
+        <v>0.1090582334119433</v>
       </c>
       <c r="M9" t="n">
-        <v>9.622379655208764</v>
+        <v>9.59954357139047</v>
       </c>
       <c r="N9" t="n">
-        <v>174.7301777188055</v>
+        <v>174.0876456893892</v>
       </c>
       <c r="O9" t="n">
-        <v>13.21855429760779</v>
+        <v>13.19422774130374</v>
       </c>
       <c r="P9" t="n">
-        <v>223.1243535149641</v>
+        <v>223.1573320783808</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27407,28 +27511,28 @@
         <v>0.1327</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04317979410512523</v>
+        <v>-0.04571178876664026</v>
       </c>
       <c r="J10" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K10" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008275420887454144</v>
+        <v>0.009314643357753782</v>
       </c>
       <c r="M10" t="n">
-        <v>2.687994733441079</v>
+        <v>2.691084484800538</v>
       </c>
       <c r="N10" t="n">
-        <v>12.87825985502603</v>
+        <v>12.86930101127665</v>
       </c>
       <c r="O10" t="n">
-        <v>3.588629244575988</v>
+        <v>3.587380800985121</v>
       </c>
       <c r="P10" t="n">
-        <v>189.3662660344063</v>
+        <v>189.3934448794605</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27479,28 +27583,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06535273059483994</v>
+        <v>-0.06604145777669393</v>
       </c>
       <c r="J11" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K11" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02000809078666366</v>
+        <v>0.0205928156956795</v>
       </c>
       <c r="M11" t="n">
-        <v>2.685654105422368</v>
+        <v>2.677938854876951</v>
       </c>
       <c r="N11" t="n">
-        <v>11.96469191837365</v>
+        <v>11.92030273786681</v>
       </c>
       <c r="O11" t="n">
-        <v>3.459001578255444</v>
+        <v>3.452579142882434</v>
       </c>
       <c r="P11" t="n">
-        <v>195.9898699362302</v>
+        <v>195.9972989113694</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27538,7 +27642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L502"/>
+  <dimension ref="A1:L504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58565,6 +58669,130 @@
         </is>
       </c>
     </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:27:02+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-46.90223922015683,168.14392690241039</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-46.90296238526304,168.14332655977168</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-46.90368216206428,168.14318639001436</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-46.904401761116034,168.14307033309586</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-46.90512035258735,168.1430912449802</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-46.9058390087321,168.1431197609876</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-46.906557330736256,168.14317632563754</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>-46.907270316731505,168.14394281656513</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>-46.907990754483826,168.14371796119923</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>-46.90870856950424,168.14384073057062</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:56+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-46.902239559902576,168.14388076670627</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-46.90296234089782,168.14333258894885</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-46.90368206564042,168.14319949709636</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-46.90440169652552,168.14307911495817</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-46.90512032173956,168.14309543935883</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-46.905838993959826,168.14312172712403</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-46.906557369144004,168.14317121361412</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>-46.90727039459607,168.1439324612985</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>-46.90799081064621,168.14371048957815</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>-46.90870864229951,168.1438308993402</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0591/nzd0591.xlsx
+++ b/data/nzd0591/nzd0591.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L504"/>
+  <dimension ref="A1:L506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21566,6 +21566,90 @@
       <c r="L504" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>187.67</v>
+      </c>
+      <c r="C505" t="n">
+        <v>160.46</v>
+      </c>
+      <c r="D505" t="n">
+        <v>150.09</v>
+      </c>
+      <c r="E505" t="n">
+        <v>140.89</v>
+      </c>
+      <c r="F505" t="n">
+        <v>140.29</v>
+      </c>
+      <c r="G505" t="n">
+        <v>141.1</v>
+      </c>
+      <c r="H505" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="I505" t="n">
+        <v>200.92</v>
+      </c>
+      <c r="J505" t="n">
+        <v>184.29</v>
+      </c>
+      <c r="K505" t="n">
+        <v>192.1</v>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>190.19</v>
+      </c>
+      <c r="C506" t="n">
+        <v>161.39</v>
+      </c>
+      <c r="D506" t="n">
+        <v>150.34</v>
+      </c>
+      <c r="E506" t="n">
+        <v>140.66</v>
+      </c>
+      <c r="F506" t="n">
+        <v>140.79</v>
+      </c>
+      <c r="G506" t="n">
+        <v>141.26</v>
+      </c>
+      <c r="H506" t="n">
+        <v>144.91</v>
+      </c>
+      <c r="I506" t="n">
+        <v>200.34</v>
+      </c>
+      <c r="J506" t="n">
+        <v>184.42</v>
+      </c>
+      <c r="K506" t="n">
+        <v>192.18</v>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21580,7 +21664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B519"/>
+  <dimension ref="A1:B521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26773,6 +26857,26 @@
       </c>
       <c r="B519" t="n">
         <v>0.12</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>-0.8</v>
       </c>
     </row>
   </sheetData>
@@ -26935,28 +27039,28 @@
         <v>0.1396</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.633921789194921</v>
+        <v>-0.65035537460168</v>
       </c>
       <c r="J2" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K2" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01978263775027655</v>
+        <v>0.02094731630014013</v>
       </c>
       <c r="M2" t="n">
-        <v>27.91910966567953</v>
+        <v>27.88946390694011</v>
       </c>
       <c r="N2" t="n">
-        <v>1134.659956917109</v>
+        <v>1131.866128909127</v>
       </c>
       <c r="O2" t="n">
-        <v>33.68471399488364</v>
+        <v>33.64321817111328</v>
       </c>
       <c r="P2" t="n">
-        <v>227.206494295376</v>
+        <v>227.3856798222598</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27007,28 +27111,28 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.171318035615845</v>
+        <v>-0.1725923343920923</v>
       </c>
       <c r="J3" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K3" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04868630909075433</v>
+        <v>0.04977310403254409</v>
       </c>
       <c r="M3" t="n">
-        <v>4.097404415895702</v>
+        <v>4.087161789826223</v>
       </c>
       <c r="N3" t="n">
-        <v>32.97462331504667</v>
+        <v>32.8555916895091</v>
       </c>
       <c r="O3" t="n">
-        <v>5.742353464830137</v>
+        <v>5.731979735615706</v>
       </c>
       <c r="P3" t="n">
-        <v>167.2325058879367</v>
+        <v>167.2462565943163</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27079,28 +27183,28 @@
         <v>0.0935</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3442778348188497</v>
+        <v>-0.3420926566056122</v>
       </c>
       <c r="J4" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K4" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L4" t="n">
-        <v>0.391917632940217</v>
+        <v>0.3902587238894357</v>
       </c>
       <c r="M4" t="n">
-        <v>2.635847447524972</v>
+        <v>2.635416911962775</v>
       </c>
       <c r="N4" t="n">
-        <v>10.574077975958</v>
+        <v>10.56365411214054</v>
       </c>
       <c r="O4" t="n">
-        <v>3.251780739219359</v>
+        <v>3.250177550864035</v>
       </c>
       <c r="P4" t="n">
-        <v>156.7384706878854</v>
+        <v>156.7148831645766</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27151,28 +27255,28 @@
         <v>0.0799</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4161379690041014</v>
+        <v>-0.4139519178941058</v>
       </c>
       <c r="J5" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K5" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L5" t="n">
-        <v>0.447300828222438</v>
+        <v>0.4462262462507762</v>
       </c>
       <c r="M5" t="n">
-        <v>2.742009891072001</v>
+        <v>2.74231954824422</v>
       </c>
       <c r="N5" t="n">
-        <v>12.30327054124856</v>
+        <v>12.28600674447051</v>
       </c>
       <c r="O5" t="n">
-        <v>3.507601821935974</v>
+        <v>3.505140046342015</v>
       </c>
       <c r="P5" t="n">
-        <v>149.253813948845</v>
+        <v>149.2302189598101</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27223,28 +27327,28 @@
         <v>0.07340000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2265675509855387</v>
+        <v>-0.2274845164234482</v>
       </c>
       <c r="J6" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K6" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1889448147521705</v>
+        <v>0.191466237203426</v>
       </c>
       <c r="M6" t="n">
-        <v>2.747881289771138</v>
+        <v>2.742711349352377</v>
       </c>
       <c r="N6" t="n">
-        <v>12.66973770017501</v>
+        <v>12.62534735841897</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55945750082439</v>
+        <v>3.553216480657908</v>
       </c>
       <c r="P6" t="n">
-        <v>147.8845330569851</v>
+        <v>147.8944285414063</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27295,28 +27399,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2161932589730642</v>
+        <v>-0.2183384236275906</v>
       </c>
       <c r="J7" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K7" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1999709599343968</v>
+        <v>0.2041099770890877</v>
       </c>
       <c r="M7" t="n">
-        <v>2.478950975612968</v>
+        <v>2.481842835452694</v>
       </c>
       <c r="N7" t="n">
-        <v>10.75176820256141</v>
+        <v>10.73947030290399</v>
       </c>
       <c r="O7" t="n">
-        <v>3.278988899426379</v>
+        <v>3.277113104991036</v>
       </c>
       <c r="P7" t="n">
-        <v>149.8373132852091</v>
+        <v>149.8604671007488</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27367,28 +27471,28 @@
         <v>0.1121</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2976870738176314</v>
+        <v>-0.2987064891239898</v>
       </c>
       <c r="J8" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K8" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2445891664842199</v>
+        <v>0.2473995489666272</v>
       </c>
       <c r="M8" t="n">
-        <v>2.922804780091113</v>
+        <v>2.914973438196773</v>
       </c>
       <c r="N8" t="n">
-        <v>15.73702816330013</v>
+        <v>15.68153527855518</v>
       </c>
       <c r="O8" t="n">
-        <v>3.966992332145367</v>
+        <v>3.95999182809197</v>
       </c>
       <c r="P8" t="n">
-        <v>154.3215596343467</v>
+        <v>154.3325629323288</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27439,28 +27543,28 @@
         <v>0.0152</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6056959357609428</v>
+        <v>-0.6103725850455772</v>
       </c>
       <c r="J9" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K9" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1090582334119433</v>
+        <v>0.1113360348574862</v>
       </c>
       <c r="M9" t="n">
-        <v>9.59954357139047</v>
+        <v>9.585004438270946</v>
       </c>
       <c r="N9" t="n">
-        <v>174.0876456893892</v>
+        <v>173.533571674328</v>
       </c>
       <c r="O9" t="n">
-        <v>13.19422774130374</v>
+        <v>13.17321417400962</v>
       </c>
       <c r="P9" t="n">
-        <v>223.1573320783808</v>
+        <v>223.2077487843359</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27511,28 +27615,28 @@
         <v>0.1327</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04571178876664026</v>
+        <v>-0.04863723493906122</v>
       </c>
       <c r="J10" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K10" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009314643357753782</v>
+        <v>0.01057681476619554</v>
       </c>
       <c r="M10" t="n">
-        <v>2.691084484800538</v>
+        <v>2.696403403897788</v>
       </c>
       <c r="N10" t="n">
-        <v>12.86930101127665</v>
+        <v>12.87472964859062</v>
       </c>
       <c r="O10" t="n">
-        <v>3.587380800985121</v>
+        <v>3.58813735085359</v>
       </c>
       <c r="P10" t="n">
-        <v>189.3934448794605</v>
+        <v>189.4249780564193</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27583,28 +27687,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06604145777669393</v>
+        <v>-0.06764058181270005</v>
       </c>
       <c r="J11" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K11" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0205928156956795</v>
+        <v>0.02173579850046325</v>
       </c>
       <c r="M11" t="n">
-        <v>2.677938854876951</v>
+        <v>2.674261899670283</v>
       </c>
       <c r="N11" t="n">
-        <v>11.92030273786681</v>
+        <v>11.88943190323719</v>
       </c>
       <c r="O11" t="n">
-        <v>3.452579142882434</v>
+        <v>3.448105552798114</v>
       </c>
       <c r="P11" t="n">
-        <v>195.9972989113694</v>
+        <v>196.0146160446131</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27642,7 +27746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L504"/>
+  <dimension ref="A1:L506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58793,6 +58897,130 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-46.90224118984328,168.14365939397928</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-46.90296247688584,168.14331410821023</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-46.90368213892268,168.14318953571404</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-46.90440168784913,168.14308029461134</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-46.90512040753461,168.14308377374334</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-46.90583911410668,168.14310573588108</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-46.90655740164268,168.1431668880558</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>-46.907270544408796,168.14391253724133</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>-46.907990845131664,168.14370590174067</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>-46.90870872577037,168.1438196261961</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-46.902240946682255,168.14369242294612</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-46.90296238719196,168.14332629763356</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-46.903682114816775,168.14319281248456</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-46.9044017100221,168.14307727994216</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-46.90512035933529,168.1430903274599</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-46.90583909834986,168.14310783309327</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-46.90655740065788,168.14316701913333</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>-46.907270601573245,168.1439049346406</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>-46.907990832322795,168.1437076057946</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>-46.9087087180057,168.14382067486065</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
